--- a/data/trans_orig/P2A_ner_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2A_ner_R-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4319</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>688</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6676</t>
+          <t>6164</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8328</t>
+          <t>8078</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>74240</t>
+          <t>74682</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>81788</t>
+          <t>82300</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>87781</t>
+          <t>87776</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>158695</t>
+          <t>158945</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>165101</t>
+          <t>165695</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7868</t>
+          <t>7351</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8115</t>
+          <t>8237</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3975</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12418</t>
+          <t>12327</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>179378</t>
+          <t>179895</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>185988</t>
+          <t>185998</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>180616</t>
+          <t>180494</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>186825</t>
+          <t>187381</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>363559</t>
+          <t>363650</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>372002</t>
+          <t>372110</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7708</t>
+          <t>7754</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1606</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7884</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3767</t>
+          <t>3412</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12472</t>
+          <t>12044</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78771</t>
+          <t>78725</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85260</t>
+          <t>85259</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>95377</t>
+          <t>95260</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>101663</t>
+          <t>101655</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>177268</t>
+          <t>177696</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>185973</t>
+          <t>186328</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6891</t>
+          <t>6381</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1576</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8196</t>
+          <t>7587</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3705</t>
+          <t>3777</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12403</t>
+          <t>11797</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>144184</t>
+          <t>144694</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>149865</t>
+          <t>149873</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>139898</t>
+          <t>140507</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>146518</t>
+          <t>146811</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>286766</t>
+          <t>287372</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>295464</t>
+          <t>295392</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6795</t>
+          <t>6303</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17334</t>
+          <t>17237</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8985</t>
+          <t>9182</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21348</t>
+          <t>20637</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17985</t>
+          <t>18112</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34398</t>
+          <t>34993</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>486025</t>
+          <t>486122</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>496564</t>
+          <t>497056</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>507201</t>
+          <t>507912</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>519564</t>
+          <t>519367</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>997510</t>
+          <t>996915</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1013923</t>
+          <t>1013796</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7569</t>
+          <t>8248</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1424</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7947</t>
+          <t>7819</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>96552</t>
+          <t>95873</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>102757</t>
+          <t>102786</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>208216</t>
+          <t>208344</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>214739</t>
+          <t>214825</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>8074</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>680</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>6540</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2909</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11244</t>
+          <t>12360</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>151317</t>
+          <t>151270</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>157946</t>
+          <t>158021</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>186603</t>
+          <t>186684</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>192549</t>
+          <t>192544</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>341324</t>
+          <t>340208</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>349659</t>
+          <t>349301</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1565</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8919</t>
+          <t>8539</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4514</t>
+          <t>5069</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2181</t>
+          <t>2708</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>11292</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>89061</t>
+          <t>89441</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>96415</t>
+          <t>96112</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>97298</t>
+          <t>96743</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>189432</t>
+          <t>188501</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>197612</t>
+          <t>197085</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,64%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>734</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7152</t>
+          <t>6884</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7522</t>
+          <t>7939</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10811</t>
+          <t>11266</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>108368</t>
+          <t>108636</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>114777</t>
+          <t>114786</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>124180</t>
+          <t>123763</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>130557</t>
+          <t>130523</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>236410</t>
+          <t>235955</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>244544</t>
+          <t>244368</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9022</t>
+          <t>8788</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21847</t>
+          <t>22044</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13079</t>
+          <t>12722</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14645</t>
+          <t>14501</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30019</t>
+          <t>30036</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>455118</t>
+          <t>454921</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>467943</t>
+          <t>468177</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>525702</t>
+          <t>526059</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>534764</t>
+          <t>534828</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>985727</t>
+          <t>985710</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1001101</t>
+          <t>1001245</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>476</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4995</t>
+          <t>4789</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>786</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7181</t>
+          <t>7300</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9311</t>
+          <t>8937</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97709</t>
+          <t>97915</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>102227</t>
+          <t>102228</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>91086</t>
+          <t>90967</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>97477</t>
+          <t>97481</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>191660</t>
+          <t>192034</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>199000</t>
+          <t>199051</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7552</t>
+          <t>7725</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5870</t>
+          <t>6007</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16499</t>
+          <t>16192</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9129</t>
+          <t>8653</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21980</t>
+          <t>21749</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>148713</t>
+          <t>148540</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>154980</t>
+          <t>154976</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>194093</t>
+          <t>194400</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>204585</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>344877</t>
+          <t>345108</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>357728</t>
+          <t>358204</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,64%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4318</t>
+          <t>4504</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13415</t>
+          <t>13604</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>4299</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13401</t>
+          <t>13610</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10866</t>
+          <t>10573</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24029</t>
+          <t>23456</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>130899</t>
+          <t>130710</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>139996</t>
+          <t>139810</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>118770</t>
+          <t>118561</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>128042</t>
+          <t>127872</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>252456</t>
+          <t>253029</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>265619</t>
+          <t>265912</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,18%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7347</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18487</t>
+          <t>18744</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2863</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11191</t>
+          <t>11015</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12092</t>
+          <t>12134</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25697</t>
+          <t>26401</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>103619</t>
+          <t>103362</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>114759</t>
+          <t>114105</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>118813</t>
+          <t>118989</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>127141</t>
+          <t>127166</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>226413</t>
+          <t>225709</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>240018</t>
+          <t>239976</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,19%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18735</t>
+          <t>19551</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35273</t>
+          <t>35676</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19518</t>
+          <t>19984</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36715</t>
+          <t>37235</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42709</t>
+          <t>41585</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>65880</t>
+          <t>65626</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>490117</t>
+          <t>489714</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>506655</t>
+          <t>505839</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>534318</t>
+          <t>533798</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>551515</t>
+          <t>551049</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1030543</t>
+          <t>1030797</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1053714</t>
+          <t>1054838</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>1679</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8187</t>
+          <t>8060</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>387</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>3940</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2339</t>
+          <t>2598</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8991</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49324</t>
+          <t>49451</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55780</t>
+          <t>55832</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57596</t>
+          <t>57504</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61056</t>
+          <t>61057</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>109964</t>
+          <t>109932</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116616</t>
+          <t>116357</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,82%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5476</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14913</t>
+          <t>14740</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6382</t>
+          <t>6333</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16560</t>
+          <t>16945</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14067</t>
+          <t>13765</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28887</t>
+          <t>27993</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>144386</t>
+          <t>144559</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>153823</t>
+          <t>153897</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>165994</t>
+          <t>165609</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>176172</t>
+          <t>176221</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>312966</t>
+          <t>313860</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>327786</t>
+          <t>328088</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>6922</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19353</t>
+          <t>18866</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4839</t>
+          <t>4714</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15685</t>
+          <t>15849</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14269</t>
+          <t>13989</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30110</t>
+          <t>30376</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>154535</t>
+          <t>155022</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>166601</t>
+          <t>166966</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>196805</t>
+          <t>196641</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>207651</t>
+          <t>207776</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>356268</t>
+          <t>356002</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>372109</t>
+          <t>372389</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,38%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5947</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17369</t>
+          <t>17633</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15693</t>
+          <t>15345</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33068</t>
+          <t>32955</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23895</t>
+          <t>24337</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45356</t>
+          <t>45429</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>258089</t>
+          <t>257825</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>269511</t>
+          <t>269341</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>272415</t>
+          <t>272528</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>289790</t>
+          <t>290138</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>535584</t>
+          <t>535511</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>557045</t>
+          <t>556603</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26948</t>
+          <t>27771</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46707</t>
+          <t>47056</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33070</t>
+          <t>33568</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55711</t>
+          <t>56348</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65472</t>
+          <t>65345</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>95484</t>
+          <t>95924</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>619448</t>
+          <t>619099</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>639207</t>
+          <t>638384</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>706261</t>
+          <t>705624</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>728902</t>
+          <t>728404</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1332643</t>
+          <t>1332203</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1362655</t>
+          <t>1362782</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">

--- a/data/trans_orig/P2A_ner_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2A_ner_R-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2696</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6156</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,05%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6,96%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1275</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3877</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4224</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,62%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,94%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2696</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>688</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6164</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8078</t>
+          <t>8125</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -836,74 +836,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>85768</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>82308</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>87781</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,95%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>93,04%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,23%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>77284</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>74682</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>74335</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>78559</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,38%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,06%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>94,62%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>85768</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>82300</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>87776</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,95%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>93,03%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>99,22%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>245</t>
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>158945</t>
+          <t>158898</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>165695</t>
+          <t>165690</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>88464</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>88464</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>88464</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>78559</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>78559</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>78559</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>88464</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>88464</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>88464</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4022</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1376</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8114</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,3%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>3231</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1248</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7351</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1261</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7712</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,73%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,67%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,93%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4022</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1350</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8237</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>3279</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12327</t>
+          <t>12337</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1179,74 +1179,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>184709</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>180617</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>187355</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,87%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>95,7%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,27%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>184015</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>179895</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>185998</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>179534</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>185985</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,27%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,07%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>95,88%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>99,33%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>184709</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>180494</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>187381</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,87%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>95,64%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,28%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>552</t>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>363650</t>
+          <t>363640</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>372110</t>
+          <t>372698</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>188731</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>188731</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>188731</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>279</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>187246</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>187246</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>187246</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>188731</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>188731</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>188731</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3859</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1291</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7491</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,25%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3344</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1220</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7754</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1198</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7542</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,87%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,97%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3859</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1606</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8001</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,74%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3412</t>
+          <t>3986</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12044</t>
+          <t>13088</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>99402</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>95770</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>101970</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,26%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>92,75%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,75%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>83135</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>78725</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>85259</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>78937</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>85281</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,13%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>91,03%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,59%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>99402</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>95260</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>101655</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,26%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>177696</t>
+          <t>176652</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>186328</t>
+          <t>185754</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>103261</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>103261</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>103261</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>86479</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>86479</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>86479</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>103261</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>103261</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>103261</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3872</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1281</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7865</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,61%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,31%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>3150</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1202</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6381</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6917</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,08%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,8%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,22%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3872</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1283</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7587</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3777</t>
+          <t>3773</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11797</t>
+          <t>12145</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -1865,74 +1865,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>144222</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>140229</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>146813</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,39%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>94,69%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,14%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>147925</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>144694</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>149873</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>144158</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>149860</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,92%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,78%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>95,42%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,2%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>144222</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>140507</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>146811</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,39%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>94,88%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,13%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>433</t>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>287372</t>
+          <t>287024</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>295392</t>
+          <t>295396</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>148094</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>148094</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>148094</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>151075</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>151075</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>151075</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>148094</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>148094</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>148094</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>14449</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>9318</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>21718</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,11%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>11000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>6303</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>17237</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>6875</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>17028</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2,19%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>14449</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>9182</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>20637</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18112</t>
+          <t>18219</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34993</t>
+          <t>34190</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>770</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>514100</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>506831</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>519231</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,27%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,89%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,24%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>729</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>492359</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>486122</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>497056</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>486331</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>496484</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>97,81%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96,58%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,75%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>770</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>514100</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>507912</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>519367</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,27%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>996915</t>
+          <t>997718</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1013796</t>
+          <t>1013689</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>746</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>3537</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1335</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8248</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1351</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7916</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,4%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,92%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7819</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>112043</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>149</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>100584</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>95873</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>102786</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>96205</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>102770</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>96,6%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>92,08%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,72%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>112043</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>208344</t>
+          <t>208057</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>214825</t>
+          <t>214822</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>112043</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>112043</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>112043</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>104121</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>104121</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>104121</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>112043</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>112043</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>112043</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2651</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6552</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,39%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>3631</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1323</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8074</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1428</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>8327</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,28%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,07%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2651</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6540</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3267</t>
+          <t>3366</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12360</t>
+          <t>12299</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>190573</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>186672</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>192571</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,63%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,61%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,66%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>155713</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>151270</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>158021</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>151017</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>157916</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,72%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>94,93%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,17%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>190573</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>186684</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>192544</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,63%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>340208</t>
+          <t>340269</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>349301</t>
+          <t>349202</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>193224</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>193224</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>193224</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>159344</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>159344</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>159344</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>193224</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>193224</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>193224</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1486</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4616</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,53%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4198</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1868</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8539</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1529</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8484</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>4,28%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,71%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1486</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5069</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2708</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11292</t>
+          <t>10897</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>100326</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>97196</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>101812</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,54%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,47%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>93782</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>89441</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>96112</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>89496</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>96451</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>95,72%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>91,29%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,09%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>100326</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>96743</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>101812</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,54%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>188501</t>
+          <t>188896</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>197085</t>
+          <t>197326</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>101812</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>101812</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>101812</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>97980</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>97980</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>97980</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>101812</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>101812</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>101812</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3263</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1152</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7267</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,48%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,52%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2820</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>734</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6884</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>736</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6644</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,44%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,64%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3263</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1179</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7939</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2853</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11266</t>
+          <t>10792</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -3812,74 +3812,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>128439</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>124435</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>130550</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,52%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>94,48%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,13%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>160</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>112700</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>108636</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>114786</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>108876</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>114784</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,56%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>94,04%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>94,25%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,36%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>128439</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>123763</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>130523</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,52%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>93,97%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>349</t>
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>235955</t>
+          <t>236429</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>244368</t>
+          <t>244458</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>131702</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>131702</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>131702</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>115520</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>115520</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>115520</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>131702</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>131702</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>131702</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7400</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3583</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>12897</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>14185</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>8788</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>22044</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>9196</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>21670</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2,97%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,62%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>7400</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>3953</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>12722</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14501</t>
+          <t>15435</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30036</t>
+          <t>30955</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>758</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>531381</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>525884</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>535198</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,63%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,61%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,33%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>667</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>462780</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>454921</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>468177</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>455295</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>467769</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>97,03%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,38%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,16%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>758</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>531381</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>526059</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>534828</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,63%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>985710</t>
+          <t>984791</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1001245</t>
+          <t>1000311</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2869</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>716</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6989</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,11%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1739</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>476</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4789</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4504</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,69%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,66%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2869</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>786</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7300</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8937</t>
+          <t>9165</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -4730,74 +4730,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>95398</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>91278</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>97551</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,08%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>92,89%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,27%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>100965</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>97915</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>102228</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>98200</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>102234</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,31%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,34%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,61%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>99,54%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>95398</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>90967</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>97481</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,08%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>92,57%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>99,2%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>307</t>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>192034</t>
+          <t>191806</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>199051</t>
+          <t>199028</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>98267</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>98267</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>98267</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>102704</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>102704</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>102704</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>98267</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>98267</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>98267</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10415</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6018</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>16682</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,86%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,92%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>3783</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1289</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7725</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1314</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7697</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,42%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,94%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>10415</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>6007</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>16192</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,95%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8653</t>
+          <t>8163</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21749</t>
+          <t>21588</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>200177</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>193910</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>204574</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,05%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,08%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,14%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>152482</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>148540</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>154976</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>148568</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>154951</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,58%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,06%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,17%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>295</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>200177</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>194400</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>204585</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>95,05%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>345108</t>
+          <t>345269</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>358204</t>
+          <t>358694</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>210592</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>210592</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>210592</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>248</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>156265</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>156265</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>156265</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>210592</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>210592</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>210592</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8017</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3777</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12993</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6,07%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,86%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9,83%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>8577</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4504</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13604</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4856</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>14241</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>5,94%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,43%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>8017</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>4299</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>13610</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>6,07%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10573</t>
+          <t>11175</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23456</t>
+          <t>23537</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>124154</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>119178</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>128394</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>93,93%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>90,17%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,14%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>194</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>135737</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>130710</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>139810</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>130073</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>139458</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>94,06%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>90,57%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,88%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>124154</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>118561</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>127872</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>93,93%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>253029</t>
+          <t>252948</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>265912</t>
+          <t>265310</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>95,96%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>132171</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>132171</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>132171</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>144314</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>144314</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>144314</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>132171</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>132171</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>132171</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5787</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2867</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11382</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,45%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,76%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>12190</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>8001</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>18744</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>7544</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>18571</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>9,98%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,55%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>15,35%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5787</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2838</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>11015</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,45%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12134</t>
+          <t>11983</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26401</t>
+          <t>25776</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>124217</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>118622</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>127137</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,55%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,24%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,79%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>109916</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>103362</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>114105</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>103535</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>114562</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>90,02%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>84,65%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>93,45%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>124217</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>118989</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>127166</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,55%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>225709</t>
+          <t>226334</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>239976</t>
+          <t>240127</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,25%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>130004</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>130004</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>130004</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>122106</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>122106</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>122106</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>130004</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>130004</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>130004</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5994,67 +5994,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>27087</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>20042</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>36656</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3,51%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6,42%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>26289</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>19551</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>35676</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>19342</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>35472</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>5,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,72%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6,79%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>27087</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>19984</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>37235</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41585</t>
+          <t>43336</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>65626</t>
+          <t>66358</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>785</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>543946</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>534377</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>550991</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>95,26%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>93,58%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>96,49%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>750</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>499101</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>489714</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>505839</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>489918</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>506048</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>95,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>93,21%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>96,28%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>785</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>543946</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>533798</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>551049</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>95,26%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1030797</t>
+          <t>1030065</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1054838</t>
+          <t>1053087</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>790</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>525390</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2806</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,55%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3880</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1679</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8060</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,75%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>14,01%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>3469</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>1572</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3940</t>
+          <t>6962</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,17 +6639,17 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5202</t>
+          <t>4484</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2598</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>7802</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>49522</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>47731</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>50244</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,99%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>94,45%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,42%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>53631</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>49451</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>55832</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>93,25%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>85,99%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,08%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>60123</t>
+          <t>48621</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57504</t>
+          <t>45128</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61057</t>
+          <t>50518</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,17 +6752,17 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>113753</t>
+          <t>98143</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>109932</t>
+          <t>94825</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116357</t>
+          <t>100526</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8914</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5230</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>14456</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,66%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,32%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,18%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>9320</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>5402</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>14740</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>5,85%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,39%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,25%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10512</t>
+          <t>9365</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>5525</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16945</t>
+          <t>14732</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>19832</t>
+          <t>18280</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13765</t>
+          <t>12529</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27993</t>
+          <t>25196</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>148608</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>143066</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>152292</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,34%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>90,82%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,68%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>149979</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>144559</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>153897</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>94,15%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90,75%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,61%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>172042</t>
+          <t>136153</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>165609</t>
+          <t>130786</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>176221</t>
+          <t>139993</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>322021</t>
+          <t>284759</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>313860</t>
+          <t>277843</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>328088</t>
+          <t>290510</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,87%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9160</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4633</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>15829</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,58%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,91%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>12098</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6922</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>18866</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,96%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,85%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9070</t>
+          <t>13203</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>7924</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15849</t>
+          <t>20862</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>21168</t>
+          <t>22364</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13989</t>
+          <t>14683</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30376</t>
+          <t>30765</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>190966</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>184297</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>195493</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>95,42%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>92,09%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,69%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>161790</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>155022</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>166966</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>93,04%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>89,15%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,02%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>203420</t>
+          <t>162315</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>196641</t>
+          <t>154656</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>207776</t>
+          <t>167594</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>365210</t>
+          <t>353280</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>356002</t>
+          <t>344879</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>372389</t>
+          <t>360961</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,09%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>386378</t>
+          <t>375644</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>386378</t>
+          <t>375644</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>386378</t>
+          <t>375644</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>23238</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>15300</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>33532</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7,94%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,23%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11,46%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>10763</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>6117</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>17633</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3,91%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,4%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22951</t>
+          <t>11281</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15345</t>
+          <t>6539</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32955</t>
+          <t>18608</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>33714</t>
+          <t>34519</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24337</t>
+          <t>24090</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45429</t>
+          <t>46353</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>269407</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>259113</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>277345</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>92,06%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>88,54%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,77%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>326</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>264695</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>257825</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>269341</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>96,09%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,6%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,78%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>282532</t>
+          <t>245272</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>272528</t>
+          <t>237945</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>290138</t>
+          <t>250014</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>547226</t>
+          <t>514679</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>535511</t>
+          <t>502845</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>556603</t>
+          <t>525108</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>42328</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>31498</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>55840</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,04%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4,49%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>7,97%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>36062</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>27771</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>47056</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5,41%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>43855</t>
+          <t>37319</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33568</t>
+          <t>28185</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56348</t>
+          <t>48112</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>79916</t>
+          <t>79646</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65345</t>
+          <t>65216</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>95924</t>
+          <t>95923</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>917</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>658501</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>644989</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>669331</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>93,96%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>92,03%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>95,51%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>888</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>630093</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>619099</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>638384</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>94,59%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>92,94%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>95,83%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>917</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>718117</t>
+          <t>592359</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>705624</t>
+          <t>581566</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>728404</t>
+          <t>601493</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1348211</t>
+          <t>1250862</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1332203</t>
+          <t>1234585</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1362782</t>
+          <t>1265292</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,1%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>943</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
